--- a/data/projects/chem/REPORT.xlsx
+++ b/data/projects/chem/REPORT.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="코드마스터" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조치검증" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판정대장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="처분대장" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -730,171 +731,342 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>JD-01</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>관련</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>설비 (SW)</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>로그 + 재현시험</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>합의완료</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>JD-02</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>관련</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>설비 (부품)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>로그 + 영상</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>합의완료</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>JD-03</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>비관련</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>자재 (로트 불량)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>로트 검사성적서</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>합의완료</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>JD-04</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>비관련</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>운영 (조작)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>CCTV + 교육 기록</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>합의완료</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>JD-05</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>판정중</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>로그 분석 중</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>합동리뷰 07-15</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="4" min="1" max="1"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="14" customWidth="1" style="4" min="3" max="3"/>
+    <col width="56" customWidth="1" style="4" min="4" max="4"/>
+    <col width="13" customWidth="1" style="4" min="5" max="5"/>
+    <col width="10" customWidth="1" style="4" min="6" max="6"/>
+    <col width="16" customWidth="1" style="4" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>처분ID</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>대상ID</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>처분</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>기한</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>오너</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>합의</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JD-01</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+          <t>DSP-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ERR-002</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>관련</t>
+          <t>carry-over</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>설비 (SW)</t>
+          <t>그립 실패 재발 원인 규명 중 — 운영 초기 집중 모니터링 조건부 이관</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>로그 + 재현시험</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>합의완료</t>
+          <t>양OO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>이관심의 상정</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JD-02</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>DSP-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ERR-001</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>관련</t>
+          <t>종결예정</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>설비 (부품)</t>
+          <t>카메라 버퍼 조치 무발생 검증 진행 중 — 심의 전 종결 예상</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>로그 + 영상</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>김OO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>합의완료</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JD-03</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>DSP-03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ERR-005</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>비관련</t>
+          <t>waiver</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>자재 (로트 불량)</t>
+          <t>경미·자가복구(센서 노이즈) — 위험수용, 월간 모니터링 조건</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>로트 검사성적서</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>박OO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>합의완료</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>JD-04</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>비관련</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>운영 (조작)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CCTV + 교육 기록</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>합의완료</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>JD-05</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>판정중</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>로그 분석 중</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>합동리뷰 07-15</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
